--- a/config/配置编辑器.xlsx
+++ b/config/配置编辑器.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -154,6 +154,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -80318,7 +80327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -80331,9 +80340,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -80348,9 +80354,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -80400,9 +80403,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -80494,9 +80494,6 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-    </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -80553,9 +80550,6 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-    </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -80612,9 +80606,6 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-    </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -80657,9 +80648,6 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
@@ -80747,12 +80735,9 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 注意: 本 sheet 只控制「列映射」；文件名/引擎/金额乘数(金额除数)/过客户白名单等仍在 JSON 里改</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
+          <t xml:space="preserve">   - 注意: 本 sheet 只控制「列映射」；文件名/引擎/金额乘数(金额除数)/过客户白名单等仍在 JSON 里改（金额单位换算见第 9 节）</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -80765,6 +80750,62 @@
       <c r="A68" t="inlineStr">
         <is>
           <t xml:space="preserve">   字段映射写回后 cleaning_config.json 会统一为标准 2 空格缩进格式（写前自动备份到 logs/）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>9. 金额单位（元 / 万元）— 由 JSON 的「金额乘数」控制（2026-09-28 更新）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 各来源当前单位: 财务端 收入.xlsx / 回款.xlsx = 元 ｜ 广东公司 = 万元 ｜ 湖南公司 = 万元 ｜ 南方韶关 = 元（整文件：收入+回款，2026-09-28 起） ｜ 运营端 = 元 ｜ 手工指标表 = 万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 换算规则: 清洗后统一输出「元」；金额乘数 1 = 源文件已是元，10000 = 源文件是万元（渲染层再 ÷10000 显示为万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 改法（改 JSON，勿在本 Excel 改）: 数据源.&lt;数据源&gt;.&lt;来源&gt;.金额乘数 = 数字（该来源所有 Sheet 相同）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     按 Sheet 不同时写字典，如 {"收入": 1, "回款": 10000}（收入已是元、回款是万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 变更记录: 2026-09-28 南方韶关 收入+回款 两个 Sheet 单位均改为「元」→ 金额乘数由 {收入:1, 回款:10000} 简化为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - ⚠ 本编辑器「字段映射」sheet 的候选列名（如 金额(元) / 金额(万元)）只决定「能否匹配上源文件列名」，不参与单位换算；</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     名字对上了但单位没同步改「金额乘数」，金额会差 10000 倍</t>
         </is>
       </c>
     </row>
@@ -80847,39 +80888,39 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>创建日期</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>审核日期</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr"/>
+      <c r="H2" s="17" t="inlineStr"/>
+      <c r="I2" s="18" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
@@ -80887,39 +80928,39 @@
       <c r="J2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>客户.名称</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>客户.姓名</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr"/>
-      <c r="H3" s="10" t="inlineStr"/>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr"/>
+      <c r="H3" s="17" t="inlineStr"/>
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>客户.名称</t>
         </is>
@@ -80927,43 +80968,43 @@
       <c r="J3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>不含税金额</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>含税金额</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>含税金额总计</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr"/>
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>不含税金额</t>
         </is>
@@ -80971,35 +81012,35 @@
       <c r="J4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>成本中心.名称</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>成本中心</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr"/>
+      <c r="G5" s="17" t="inlineStr"/>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>成本中心</t>
         </is>
@@ -81011,31 +81052,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr"/>
+      <c r="F6" s="17" t="inlineStr"/>
+      <c r="G6" s="17" t="inlineStr"/>
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
@@ -81047,31 +81088,31 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>排除标记</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>初始化</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>初始化</t>
         </is>
@@ -81083,35 +81124,35 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>业务日期</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="17" t="inlineStr"/>
+      <c r="H8" s="17" t="inlineStr"/>
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>业务日期</t>
         </is>
@@ -81119,43 +81160,43 @@
       <c r="J8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>付款人(客户).名称</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>付款人名称</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>付款人(客户).姓名</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>客户.名称</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr"/>
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>付款人(客户).名称</t>
         </is>
@@ -81163,43 +81204,43 @@
       <c r="J9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>应收金额</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>实收</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>收款金额</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr"/>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>应收金额</t>
         </is>
@@ -81207,35 +81248,35 @@
       <c r="J10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>成本中心.名称</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>成本中心</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr"/>
-      <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr"/>
+      <c r="G11" s="17" t="inlineStr"/>
+      <c r="H11" s="17" t="inlineStr"/>
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>成本中心.名称</t>
         </is>
@@ -81243,35 +81284,35 @@
       <c r="J11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>收款公司</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="10" t="inlineStr"/>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr"/>
+      <c r="G12" s="17" t="inlineStr"/>
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>收款公司</t>
         </is>
@@ -81283,31 +81324,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>收款日期</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>收款日期</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr"/>
-      <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr"/>
-      <c r="H13" s="10" t="inlineStr"/>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr"/>
+      <c r="F13" s="17" t="inlineStr"/>
+      <c r="G13" s="17" t="inlineStr"/>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>收款日期</t>
         </is>
@@ -81319,35 +81360,35 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>广东公司</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr"/>
+      <c r="G14" s="17" t="inlineStr"/>
+      <c r="H14" s="17" t="inlineStr"/>
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -81355,35 +81396,35 @@
       <c r="J14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>广东公司</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr"/>
+      <c r="G15" s="17" t="inlineStr"/>
+      <c r="H15" s="17" t="inlineStr"/>
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
@@ -81391,35 +81432,35 @@
       <c r="J15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>广东公司</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>金额(万元)</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="15" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr"/>
+      <c r="G16" s="17" t="inlineStr"/>
+      <c r="H16" s="17" t="inlineStr"/>
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
@@ -81427,35 +81468,35 @@
       <c r="J16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>湖南公司</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr"/>
+      <c r="G17" s="17" t="inlineStr"/>
+      <c r="H17" s="17" t="inlineStr"/>
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -81463,35 +81504,35 @@
       <c r="J17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>湖南公司</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr"/>
+      <c r="G18" s="17" t="inlineStr"/>
+      <c r="H18" s="17" t="inlineStr"/>
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
@@ -81499,35 +81540,35 @@
       <c r="J18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>湖南公司</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>金额(万元)</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr"/>
+      <c r="G19" s="17" t="inlineStr"/>
+      <c r="H19" s="17" t="inlineStr"/>
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
@@ -81535,35 +81576,35 @@
       <c r="J19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>南方韶关</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="15" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr"/>
+      <c r="G20" s="17" t="inlineStr"/>
+      <c r="H20" s="17" t="inlineStr"/>
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -81571,35 +81612,35 @@
       <c r="J20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>南方韶关</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr"/>
+      <c r="G21" s="17" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr"/>
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
@@ -81607,35 +81648,35 @@
       <c r="J21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>财务端</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>南方韶关</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>金额(万元)</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>金额(元)</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr"/>
+      <c r="G22" s="17" t="inlineStr"/>
+      <c r="H22" s="17" t="inlineStr"/>
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
@@ -81643,43 +81684,43 @@
       <c r="J22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>确认时间</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>到款时间</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr"/>
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>到款时间</t>
         </is>
@@ -81691,35 +81732,35 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr"/>
+      <c r="G24" s="17" t="inlineStr"/>
+      <c r="H24" s="17" t="inlineStr"/>
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
@@ -81727,35 +81768,35 @@
       <c r="J24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr"/>
+      <c r="G25" s="17" t="inlineStr"/>
+      <c r="H25" s="17" t="inlineStr"/>
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
@@ -81767,35 +81808,35 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>事业部</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="15" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr"/>
+      <c r="G26" s="17" t="inlineStr"/>
+      <c r="H26" s="17" t="inlineStr"/>
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>事业部</t>
         </is>
@@ -81803,43 +81844,43 @@
       <c r="J26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>内部交易</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>是否属于内部交易</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>是否属于内部单位</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>是否内部交易</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>内部交易</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr"/>
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>是否属于内部单位</t>
         </is>
@@ -81851,39 +81892,39 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>核算单位</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>核算单位</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>所属单位</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr"/>
-      <c r="H28" s="10" t="inlineStr"/>
-      <c r="I28" s="15" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr"/>
+      <c r="H28" s="17" t="inlineStr"/>
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
@@ -81895,39 +81936,39 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>核算单位</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>所属单位</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr"/>
-      <c r="I29" s="15" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr"/>
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
@@ -81935,43 +81976,43 @@
       <c r="J29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>到款时间</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>确认时间</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr"/>
-      <c r="I30" s="15" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr"/>
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>到款时间</t>
         </is>
@@ -81979,35 +82020,35 @@
       <c r="J30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="15" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr"/>
+      <c r="G31" s="17" t="inlineStr"/>
+      <c r="H31" s="17" t="inlineStr"/>
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
@@ -82015,39 +82056,39 @@
       <c r="J31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>到款</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr"/>
+      <c r="H32" s="17" t="inlineStr"/>
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
@@ -82059,35 +82100,35 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>事业部</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
-      <c r="I33" s="15" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr"/>
+      <c r="G33" s="17" t="inlineStr"/>
+      <c r="H33" s="17" t="inlineStr"/>
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>事业部</t>
         </is>
@@ -82095,43 +82136,43 @@
       <c r="J33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>内部交易</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>是否属于内部款项</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>是否属于内部单位</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>是否内部款项</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>内部款项</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr"/>
-      <c r="I34" s="15" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr"/>
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>是否属于内部单位</t>
         </is>
@@ -82143,39 +82184,39 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>核算单位</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>核算单位</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>所属单位</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr"/>
-      <c r="H35" s="10" t="inlineStr"/>
-      <c r="I35" s="15" t="inlineStr">
+      <c r="G35" s="17" t="inlineStr"/>
+      <c r="H35" s="17" t="inlineStr"/>
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
@@ -82187,39 +82228,39 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>运营端</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>回款</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>核算单位</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>所属单位</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr"/>
-      <c r="H36" s="10" t="inlineStr"/>
-      <c r="I36" s="15" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr"/>
+      <c r="H36" s="17" t="inlineStr"/>
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>法人主体</t>
         </is>

--- a/config/配置编辑器.xlsx
+++ b/config/配置编辑器.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -229,6 +229,10 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="48">
@@ -510,7 +514,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -689,6 +693,50 @@
         <color rgb="00B0B7C3"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B7C3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B7C3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B7C3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B7C3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B7C3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B7C3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B7C3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B7C3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
@@ -837,7 +885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -918,6 +966,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1620,11 +1671,11 @@
           <t>数据总览</t>
         </is>
       </c>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
+      <c r="C3" s="30" t="n"/>
+      <c r="D3" s="30" t="n"/>
+      <c r="E3" s="30" t="n"/>
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="31" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="26" t="n">
@@ -1664,11 +1715,11 @@
           <t>年度达成</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="26" t="n">
@@ -2478,11 +2529,11 @@
           <t>月度达成</t>
         </is>
       </c>
-      <c r="C29" s="25" t="n"/>
-      <c r="D29" s="25" t="n"/>
-      <c r="E29" s="25" t="n"/>
-      <c r="F29" s="25" t="n"/>
-      <c r="G29" s="25" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="30" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="31" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="26" t="n">
@@ -2623,11 +2674,11 @@
           <t>季度达成</t>
         </is>
       </c>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="25" t="n"/>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="25" t="n"/>
-      <c r="G34" s="25" t="n"/>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="31" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="26" t="n">
@@ -2768,11 +2819,11 @@
           <t>销售达成</t>
         </is>
       </c>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="25" t="n"/>
-      <c r="G39" s="25" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="30" t="n"/>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="31" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="23" t="n"/>
@@ -2781,11 +2832,11 @@
           <t>年度同比</t>
         </is>
       </c>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="25" t="n"/>
-      <c r="G40" s="25" t="n"/>
+      <c r="C40" s="30" t="n"/>
+      <c r="D40" s="30" t="n"/>
+      <c r="E40" s="30" t="n"/>
+      <c r="F40" s="30" t="n"/>
+      <c r="G40" s="31" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="26" t="n">
@@ -2914,7 +2965,7 @@
     <mergeCell ref="B39:G39"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="E7 E31 E36 E42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="怎么填" prompt="三选一：目标合计降序 / 实际金额降序 / 达成率降序" type="list">
+    <dataValidation sqref="E7 E31 E36 E42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="怎么填" prompt="四选一：目标合计降序 / 实际金额降序 / 达成率降序 / 不排序（按指标表顺序）" type="list">
       <formula1>"目标合计降序,实际金额降序,达成率降序,不排序（按指标表顺序）"</formula1>
     </dataValidation>
     <dataValidation sqref="E4 E6 E30 E35 E41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="怎么填" prompt="整数 ≥ 0；0 = 不限（显示全部）" type="whole" operator="greaterThanOrEqual">
@@ -83351,7 +83402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A82"/>
+  <dimension ref="A1:A87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -83364,9 +83415,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -83402,9 +83451,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
@@ -83454,9 +83501,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
+    <row r="16"/>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -83502,7 +83547,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 排序: 下拉三选一（目标合计降序 / 实际金额降序 / 达成率降序）</t>
+          <t xml:space="preserve">      · 排序: 下拉四选一（目标合计降序 / 实际金额降序 / 达成率降序 / 不排序（按指标表顺序））；不排序 = 完全按指标表行序，此时「优先展示」只决定可见性、不改顺序</t>
         </is>
       </c>
     </row>
@@ -83555,9 +83600,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-    </row>
+    <row r="31"/>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
@@ -83614,282 +83657,307 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-    </row>
+    <row r="40"/>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 多组配置(同一子公司在多个母公司下)的归属规则（2026-09-28）:</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     · 广东自有客户 &lt;-&gt; 零部件客户/福建市场 等: 法人=广东汽车检测中心有限公司 → 广东自有客户; 其他法人 → 另一个父组</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     · 比亚迪汽车工业有限公司 &lt;-&gt; 比亚迪电池: **只对两父组下同时出现的子公司判断**; 法人=广东汽车检测中心 → 比亚迪汽车工业, 其他法人 → 比亚迪电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     · 其他任意两组重复配置: 无规则 → 取先出现的分组, 且弹窗明细会与矩阵行对不上（尽量避免重复配置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 核对方法: 客户矩阵某行的数字 = 该行「子公司明细」抽屉里各子行相加（两处已统一口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>5. 「KPI指标」sheet 列说明（Hero 圆环指标总数，万元）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 页面: 年度达成 / 月度达成 / 季度达成</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 指标: 收入 / 回款</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 值(万元): 填数字 = 覆盖 KPI 卡片显示的指标总数（如 50000 = 5亿）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     · 留空 = 不覆盖，KPI 卡片仍按指标文件合计（现状）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     · 不影响表格/矩阵/部门卡里的明细指标（只改 Hero 圆环总数）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 说明: 备注（可选）</t>
+          <t xml:space="preserve">   - 页面: 年度达成 / 月度达成 / 季度达成</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 注意: 数据总览页的年度 KPI 跟随「年度达成」的设置</t>
+          <t xml:space="preserve">   - 指标: 收入 / 回款</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 值(万元): 填数字 = 覆盖 KPI 卡片显示的指标总数（如 50000 = 5亿）</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>6. 常见修改：</t>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     · 留空 = 不覆盖，KPI 卡片仍按指标文件合计（现状）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 换月份: 改「时间配置」的月度数据开始/结束日期</t>
+          <t xml:space="preserve">     · 不影响表格/矩阵/部门卡里的明细指标（只改 Hero 圆环总数）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 调整优先展示客户: 「展示规则」sheet → 第 4 列 配置项 = 优先展示 的那些行（一个客户一行，可下拉选）</t>
+          <t xml:space="preserve">   - 说明: 备注（可选）</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 显示全部客户: 把 配置项 = 优先展示 的所有行的「值」清空（或删行）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 只显示指定客户: 配置项 = 客户筛选 的那些行，「值」填客户名（下拉选）；清空 = 不筛选</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">   - 注意: 数据总览页的年度 KPI 跟随「年度达成」的设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 改销售归属: 在「销售归属」sheet 直接改对应行的 销售 / 比例</t>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>6. 常见修改：</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 拆分多销售: 把一行复制成多行，各填不同销售和比例（合计需=1）</t>
+          <t xml:space="preserve">   - 换月份: 改「时间配置」的月度数据开始/结束日期</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 调整优先展示客户: 「展示规则」sheet → 第 4 列 配置项 = 优先展示 的那些行（一个客户一行，可下拉选）</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>7. 「字段映射」sheet 列说明（清洗时的字段↔列名匹配，2026-09-17 新增）：</t>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 显示全部客户: 把 配置项 = 优先展示 的所有行的「值」清空（或删行）</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 数据源: 财务端 / 运营端（勿改）</t>
+          <t xml:space="preserve">   - 只显示指定客户: 配置项 = 客户筛选 的那些行，「值」填客户名（下拉选）；清空 = 不筛选</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 来源: 收入 / 回款 / 广东公司 / 湖南公司 / 南方韶关（勿改）</t>
+          <t xml:space="preserve">   - 改销售归属: 在「销售归属」sheet 直接改对应行的 销售 / 比例</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 标准字段: 系统内部字段名（勿改）</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 候选1..候选N: 按优先级从左到右尝试匹配源文件列名；留空 = 不参与</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">   - 拆分多销售: 把一行复制成多行，各填不同销售和比例（合计需=1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     · 匹配规则是【全名精确匹配】（仅忽略首尾空白），不是关键词匹配</t>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>7. 「字段映射」sheet 列说明（清洗时的字段↔列名匹配，2026-09-17 新增）：</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 源文件列名改了，把新列名加到候选里保存即可，无需改 JSON/代码</t>
+          <t xml:space="preserve">   - 数据源: 财务端 / 运营端（勿改）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 同一字段内候选不能重复；每个字段至少保留 1 个候选</t>
+          <t xml:space="preserve">   - 来源: 收入 / 回款 / 广东公司 / 湖南公司 / 南方韶关（勿改）</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 当前命中(只读): 上次清洗实际命中的列，写回时被忽略，仅供参考</t>
+          <t xml:space="preserve">   - 标准字段: 系统内部字段名（勿改）</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 说明: 备注（可选）</t>
+          <t xml:space="preserve">   - 候选1..候选N: 按优先级从左到右尝试匹配源文件列名；留空 = 不参与</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 「排除标记」字段（仅财务端收入，回款无此字段）: 源表列名就叫「初始化」；值 = √ 的行属期初/历史单据迁移</t>
+          <t xml:space="preserve">     · 匹配规则是【全名精确匹配】（仅忽略首尾空白），不是关键词匹配</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">     清洗时整行剔除、不计入当月收入（2026-09-24 口径）；命中取值在 cleaning_config.json 的 排除标记值 里改</t>
+          <t xml:space="preserve">     · 源文件列名改了，把新列名加到候选里保存即可，无需改 JSON/代码</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 注意: 本 sheet 只控制「列映射」；文件名/引擎/金额乘数(金额除数)/过客户白名单等仍在 JSON 里改（金额单位换算见第 9 节）</t>
+          <t xml:space="preserve">     · 同一字段内候选不能重复；每个字段至少保留 1 个候选</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 当前命中(只读): 上次清洗实际命中的列，写回时被忽略，仅供参考</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>8. 校验失败时生成器拒绝写回并提示原因，JSON 保持原样。</t>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 说明: 备注（可选）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">   字段映射写回后 cleaning_config.json 会统一为标准 2 空格缩进格式（写前自动备份到 logs/）。</t>
+          <t xml:space="preserve">   - 「排除标记」字段（仅财务端收入，回款无此字段）: 源表列名就叫「初始化」；值 = √ 的行属期初/历史单据迁移</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     清洗时整行剔除、不计入当月收入（2026-09-24 口径）；命中取值在 cleaning_config.json 的 排除标记值 里改</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>9. 金额单位（元 / 万元）— 由 JSON 的「金额乘数」控制（2026-09-28 更新）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 各来源当前单位: 财务端 收入.xlsx / 回款.xlsx = 元 ｜ 广东公司 = 万元 ｜ 湖南公司 = 万元 ｜ 南方韶关 = 元（整文件：收入+回款，2026-09-28 起） ｜ 运营端 = 元 ｜ 手工指标表 = 万元</t>
-        </is>
-      </c>
-    </row>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 注意: 本 sheet 只控制「列映射」；文件名/引擎/金额乘数(金额除数)/过客户白名单等仍在 JSON 里改（金额单位换算见第 9 节）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 换算规则: 清洗后统一输出「元」；金额乘数 1 = 源文件已是元，10000 = 源文件是万元（渲染层再 ÷10000 显示为万元）</t>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>8. 校验失败时生成器拒绝写回并提示原因，JSON 保持原样。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 改法（改 JSON，勿在本 Excel 改）: 数据源.&lt;数据源&gt;.&lt;来源&gt;.金额乘数 = 数字（该来源所有 Sheet 相同）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     按 Sheet 不同时写字典，如 {"收入": 1, "回款": 10000}（收入已是元、回款是万元）</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">   字段映射写回后 cleaning_config.json 会统一为标准 2 空格缩进格式（写前自动备份到 logs/）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 变更记录: 2026-09-28 南方韶关 收入+回款 两个 Sheet 单位均改为「元」→ 金额乘数由 {收入:1, 回款:10000} 简化为 1</t>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>9. 金额单位（元 / 万元）— 由 JSON 的「金额乘数」控制（2026-09-28 更新）：</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - ⚠ 本编辑器「字段映射」sheet 的候选列名（如 金额(元) / 金额(万元)）只决定「能否匹配上源文件列名」，不参与单位换算；</t>
+          <t xml:space="preserve">   - 各来源当前单位: 财务端 收入.xlsx / 回款.xlsx = 元 ｜ 广东公司 = 万元 ｜ 湖南公司 = 万元 ｜ 南方韶关 = 元（整文件：收入+回款，2026-09-28 起） ｜ 运营端 = 元 ｜ 手工指标表 = 万元</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 换算规则: 清洗后统一输出「元」；金额乘数 1 = 源文件已是元，10000 = 源文件是万元（渲染层再 ÷10000 显示为万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 改法（改 JSON，勿在本 Excel 改）: 数据源.&lt;数据源&gt;.&lt;来源&gt;.金额乘数 = 数字（该来源所有 Sheet 相同）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     按 Sheet 不同时写字典，如 {"收入": 1, "回款": 10000}（收入已是元、回款是万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 变更记录: 2026-09-28 南方韶关 收入+回款 两个 Sheet 单位均改为「元」→ 金额乘数由 {收入:1, 回款:10000} 简化为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - ⚠ 本编辑器「字段映射」sheet 的候选列名（如 金额(元) / 金额(万元)）只决定「能否匹配上源文件列名」，不参与单位换算；</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t xml:space="preserve">     名字对上了但单位没同步改「金额乘数」，金额会差 10000 倍</t>
         </is>

--- a/config/配置编辑器.xlsx
+++ b/config/配置编辑器.xlsx
@@ -670,10 +670,10 @@
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46326.99998842592</v>
+        <v>46295.99998842592</v>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="6" t="inlineStr"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="5" t="n">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>46387.99998842592</v>
